--- a/Borrador_Aplicación.xlsx
+++ b/Borrador_Aplicación.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbc4fd79f18f5b67/Documentos/Maestría/Analítica computacional para la toma de decisiones/Proyecto_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFFD091D-AF98-416C-A602-86377F942BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="8_{BFFD091D-AF98-416C-A602-86377F942BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6944AF1B-0F05-44AE-BABA-F6ECEC7DCE53}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8C44B26D-90CA-4AE3-B000-FBA2579D263B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="12" xr2:uid="{8C44B26D-90CA-4AE3-B000-FBA2579D263B}"/>
   </bookViews>
   <sheets>
     <sheet name="PáginaPrincipal" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,14 @@
     <sheet name="Estrato Familiar" sheetId="3" r:id="rId3"/>
     <sheet name="Educación Padres" sheetId="4" r:id="rId4"/>
     <sheet name="CuartosPersonas" sheetId="5" r:id="rId5"/>
+    <sheet name="Pregunta 2" sheetId="6" r:id="rId6"/>
+    <sheet name="Municipio" sheetId="7" r:id="rId7"/>
+    <sheet name="Rural vs Urbano" sheetId="8" r:id="rId8"/>
+    <sheet name="Oficiales vs no oficiales" sheetId="9" r:id="rId9"/>
+    <sheet name="Pregunta 3" sheetId="10" r:id="rId10"/>
+    <sheet name="PorMunicipioYTecnología" sheetId="11" r:id="rId11"/>
+    <sheet name="BrechaDigital" sheetId="12" r:id="rId12"/>
+    <sheet name="DesempeñoArea" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="47">
   <si>
     <t>Pregunta 1</t>
   </si>
@@ -120,6 +128,73 @@
   <si>
     <t>Por Cuartos/ Personas que convive en el hogar</t>
   </si>
+  <si>
+    <t>Puntaje promedio por municipio</t>
+  </si>
+  <si>
+    <t>Brecha rural vs urbano</t>
+  </si>
+  <si>
+    <t>Colegios oficiales vs no oficiales</t>
+  </si>
+  <si>
+    <t>¿Existen diferencias significativas en el desempeño académico entre los municipios del departamento de Santander, y en qué medida estas diferencias podrían estar asociadas a características institucionales como naturaleza del colegio y ubicación rural o urbana?</t>
+  </si>
+  <si>
+    <t>Utilice la barra lateral para desplazarse a travez del gráfico</t>
+  </si>
+  <si>
+    <t>Aquí va el gráfico de barras horizontales</t>
+  </si>
+  <si>
+    <t>Barra para desplazarsepor el gráfico</t>
+  </si>
+  <si>
+    <t>Lista desplegable con buscador, para que el usuario pueda buscar y visualizar los municipios que concuerden con su búsqueda</t>
+  </si>
+  <si>
+    <t>Histograma del municipio seleccionado</t>
+  </si>
+  <si>
+    <t>Espacio del  histograma, que estára en blanco si el usuario no ha seleccionado nada, si seleccionó un municipio, entonces se mostrara el histograma
+El histograma debe mostrarse bajo el mismo rango de valores, es decir, que desde el "bin" con el valor más bajo hasta el "bin" con el valor más alto estáran fijos en la interfaz, lo que se movera seran las barras de histograma que seleccione el usuario</t>
+  </si>
+  <si>
+    <t>Brecha Urbano-Rural por municipio</t>
+  </si>
+  <si>
+    <t>Brecha Oficial-No oficial por Municipio</t>
+  </si>
+  <si>
+    <t>¿Existen diferencias significativas en los resultados de las Pruebas Saber 11 entre estudiantes con y sin acceso a computador e internet en el hogar, y qué tan asociadas están estas diferencias a otras características socioeconómicas y educativas?</t>
+  </si>
+  <si>
+    <t>Acceso tecnológico por municipio y tecnología</t>
+  </si>
+  <si>
+    <t>Brecha digital por municipio</t>
+  </si>
+  <si>
+    <t>Desempeño por área academica según acceso tecnológico</t>
+  </si>
+  <si>
+    <t>Aquí va el gráfico de barras verticales</t>
+  </si>
+  <si>
+    <t>Puntaje promedio por municipio y acceso tecnológico</t>
+  </si>
+  <si>
+    <t>check list para seleccionar tecnología</t>
+  </si>
+  <si>
+    <t>Aquí va el gráfico de caja y bigotes</t>
+  </si>
+  <si>
+    <t>Aquí va el gráfico mapa de calor</t>
+  </si>
+  <si>
+    <t>Checklist, para que el usuario pueda buscar y visualizar las áreas académicas</t>
+  </si>
 </sst>
 </file>
 
@@ -156,7 +231,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -244,41 +319,125 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -290,6 +449,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -304,44 +466,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -551,6 +692,618 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>289215</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFF9C240-703C-22AA-83D4-204652D41771}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9433215" y="95250"/>
+          <a:ext cx="6587835" cy="9925050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Conector recto de flecha 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7608D59D-AAF1-358D-10C2-DBA92EA168D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="6305550" y="1981200"/>
+          <a:ext cx="4219575" cy="209550"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Conector recto de flecha 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7407FB68-8ADC-4435-8A25-952CBA5527C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="6305550" y="1981200"/>
+          <a:ext cx="4219575" cy="209550"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>640606</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9CF6276-9661-4180-72BE-455BC2E2A521}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10546606" y="190500"/>
+          <a:ext cx="8427193" cy="10382250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Conector recto de flecha 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4322E9F9-2BDC-4495-B855-D6713F9050BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="6305550" y="1981200"/>
+          <a:ext cx="4219575" cy="209550"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>662324</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>723899</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{581FF7FA-CA56-B80B-66DC-4BE585FA4316}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10568324" y="0"/>
+          <a:ext cx="6919575" cy="8524875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>713199</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70816800-F416-D86D-E7EA-FE81ED9895A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8782050" y="752475"/>
+          <a:ext cx="9457149" cy="3924300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Conector recto de flecha 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D128478-250F-4EEA-9841-0687E6A1670F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="5924550" y="2066925"/>
+          <a:ext cx="2705100" cy="85725"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Conector recto de flecha 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{606EFD0B-D89E-43F6-97D0-789E0BC130A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="5924550" y="2066925"/>
+          <a:ext cx="3676650" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>317795</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A26A0079-5DA3-30E2-453E-B1C23692E991}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9461795" y="123825"/>
+          <a:ext cx="7864180" cy="17040225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Conector recto de flecha 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82335F02-C664-49B5-997C-A2ABBB182B09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="5924550" y="2066925"/>
+          <a:ext cx="3676650" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>463409</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>161924</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA71BB6F-72C6-632A-A70E-D8D0EE283EB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9607409" y="714375"/>
+          <a:ext cx="6556515" cy="3190875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -893,256 +1646,196 @@
     </row>
     <row r="3" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="6"/>
+      <c r="K3" s="5"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="6"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="5"/>
     </row>
     <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="6"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="6"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="6"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="5"/>
     </row>
     <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="6"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="5"/>
     </row>
     <row r="9" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="6"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="6"/>
+      <c r="K10" s="5"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
-      <c r="C11" s="5" t="s">
+      <c r="C11" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D13" s="12"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="10" t="s">
         <v>1</v>
       </c>
       <c r="G13" s="12"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="10" t="s">
         <v>1</v>
       </c>
       <c r="J13" s="12"/>
-      <c r="K13" s="6"/>
-      <c r="M13" s="25"/>
+      <c r="K13" s="5"/>
+      <c r="M13" s="9"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="6"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="39"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="39"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="5"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="6"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="39"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="5"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="6"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="39"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="39"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="5"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="6"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="39"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="39"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="5"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="4"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="6"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="39"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="39"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="5"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="6"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="15"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="15"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="6"/>
+      <c r="K20" s="5"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5" t="s">
+      <c r="H21" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="6"/>
+      <c r="K21" s="5"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="9"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1152,6 +1845,1131 @@
     <mergeCell ref="I13:J19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7718D647-B684-4D55-B9B8-562742196BDD}">
+  <dimension ref="B1:M22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="4"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4"/>
+      <c r="C4" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="4"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="4"/>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="4"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="F13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="I13" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" s="12"/>
+      <c r="K13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="39"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="39"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="4"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="39"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="4"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="39"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="39"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="4"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="39"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="39"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B18" s="4"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="39"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="39"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="4"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="15"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="15"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="4"/>
+      <c r="H21" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="6"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C4:J9"/>
+    <mergeCell ref="C13:D19"/>
+    <mergeCell ref="F13:G19"/>
+    <mergeCell ref="I13:J19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B05A13B-BB71-4E06-BBDB-0C82BFE8DF82}">
+  <dimension ref="B1:M28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+      <c r="C3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+      <c r="C8" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="4"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="4"/>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="4"/>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="4"/>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="4"/>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="4"/>
+      <c r="C19" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="4"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="4"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="4"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="4"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="4"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="4"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="4"/>
+      <c r="H27" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C3:J4"/>
+    <mergeCell ref="C19:J26"/>
+    <mergeCell ref="C8:J13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F04E75D-4F40-49BD-90A7-53543541C282}">
+  <dimension ref="B1:M28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+      <c r="C3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+      <c r="C8" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="4"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="4"/>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="4"/>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="4"/>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="4"/>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="4"/>
+      <c r="C19" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="4"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="4"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="4"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="4"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="4"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="4"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="4"/>
+      <c r="H27" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C3:J4"/>
+    <mergeCell ref="C8:J13"/>
+    <mergeCell ref="C19:J26"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{836F8727-0523-458A-A7B1-4256FAC43D14}">
+  <dimension ref="B1:M28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+      <c r="C3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+      <c r="C8" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="4"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="4"/>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="4"/>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="4"/>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="4"/>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="4"/>
+      <c r="C19" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="4"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="4"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="4"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="4"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="4"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="4"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="4"/>
+      <c r="H27" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C3:J4"/>
+    <mergeCell ref="C8:J13"/>
+    <mergeCell ref="C19:J26"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1175,256 +2993,196 @@
     </row>
     <row r="3" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="6"/>
+      <c r="K3" s="5"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="6"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="5"/>
     </row>
     <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="6"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="6"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="6"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="5"/>
     </row>
     <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="6"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="5"/>
     </row>
     <row r="9" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="6"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="6"/>
+      <c r="K10" s="5"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
-      <c r="C11" s="5" t="s">
+      <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="12"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="10" t="s">
         <v>7</v>
       </c>
       <c r="G13" s="12"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="10" t="s">
         <v>24</v>
       </c>
       <c r="J13" s="12"/>
-      <c r="K13" s="6"/>
-      <c r="M13" s="25"/>
+      <c r="K13" s="5"/>
+      <c r="M13" s="9"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="6"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="39"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="39"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="5"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="6"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="39"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="5"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="6"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="39"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="39"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="5"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="6"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="39"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="39"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="5"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="4"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="6"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="39"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="39"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="5"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="6"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="15"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="15"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="6"/>
+      <c r="K20" s="5"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5" t="s">
+      <c r="H21" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="6"/>
+      <c r="K21" s="5"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="9"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1457,226 +3215,212 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="4"/>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="12"/>
-      <c r="K3" s="6"/>
+      <c r="K3" s="5"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="6"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="5"/>
     </row>
     <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
-      <c r="K5" s="6"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4"/>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="6"/>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4"/>
-      <c r="K7" s="6"/>
+      <c r="K7" s="5"/>
     </row>
     <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
-      <c r="K8" s="6"/>
+      <c r="K8" s="5"/>
     </row>
     <row r="9" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
-      <c r="K9" s="6"/>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
-      <c r="K10" s="6"/>
+      <c r="K10" s="5"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
-      <c r="K13" s="6"/>
-      <c r="M13" s="25"/>
+      <c r="K13" s="5"/>
+      <c r="M13" s="9"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
-      <c r="K14" s="6"/>
+      <c r="K14" s="5"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
-      <c r="K15" s="6"/>
+      <c r="K15" s="5"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="C16" t="s">
         <v>11</v>
       </c>
-      <c r="K16" s="6"/>
+      <c r="K16" s="5"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
       <c r="C17" t="s">
         <v>12</v>
       </c>
-      <c r="K17" s="6"/>
+      <c r="K17" s="5"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4"/>
-      <c r="K18" s="6"/>
+      <c r="K18" s="5"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="4"/>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="6"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="6"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="5"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="6"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="5"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="4"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="6"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="5"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="4"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="6"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="5"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="6"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="5"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="4"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="6"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="5"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="6"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="5"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5" t="s">
+      <c r="H27" t="s">
         <v>3</v>
       </c>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="6"/>
+      <c r="K27" s="5"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="7"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="9"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1708,226 +3452,212 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="4"/>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="12"/>
-      <c r="K3" s="6"/>
+      <c r="K3" s="5"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="6"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="5"/>
     </row>
     <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
-      <c r="K5" s="6"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4"/>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="6"/>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4"/>
-      <c r="K7" s="6"/>
+      <c r="K7" s="5"/>
     </row>
     <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
-      <c r="K8" s="6"/>
+      <c r="K8" s="5"/>
     </row>
     <row r="9" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
-      <c r="K9" s="6"/>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
-      <c r="K10" s="6"/>
+      <c r="K10" s="5"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
-      <c r="K13" s="6"/>
-      <c r="M13" s="25"/>
+      <c r="K13" s="5"/>
+      <c r="M13" s="9"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
-      <c r="K14" s="6"/>
+      <c r="K14" s="5"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
-      <c r="K15" s="6"/>
+      <c r="K15" s="5"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="C16" t="s">
         <v>15</v>
       </c>
-      <c r="K16" s="6"/>
+      <c r="K16" s="5"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
       <c r="C17" t="s">
         <v>16</v>
       </c>
-      <c r="K17" s="6"/>
+      <c r="K17" s="5"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4"/>
-      <c r="K18" s="6"/>
+      <c r="K18" s="5"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="4"/>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="6"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="6"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="5"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="6"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="5"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="4"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="6"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="5"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="4"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="6"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="5"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="6"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="5"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="4"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="6"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="5"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="6"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="5"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5" t="s">
+      <c r="H27" t="s">
         <v>3</v>
       </c>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="6"/>
+      <c r="K27" s="5"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="7"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="9"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1959,226 +3689,212 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="4"/>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="12"/>
-      <c r="K3" s="6"/>
+      <c r="K3" s="5"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="6"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="5"/>
     </row>
     <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
-      <c r="K5" s="6"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4"/>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="6"/>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4"/>
-      <c r="K7" s="6"/>
+      <c r="K7" s="5"/>
     </row>
     <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
-      <c r="K8" s="6"/>
+      <c r="K8" s="5"/>
     </row>
     <row r="9" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
-      <c r="K9" s="6"/>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
-      <c r="K10" s="6"/>
+      <c r="K10" s="5"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
-      <c r="K13" s="6"/>
-      <c r="M13" s="25"/>
+      <c r="K13" s="5"/>
+      <c r="M13" s="9"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
-      <c r="K14" s="6"/>
+      <c r="K14" s="5"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
-      <c r="K15" s="6"/>
+      <c r="K15" s="5"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="C16" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="6"/>
+      <c r="K16" s="5"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
       <c r="C17" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="6"/>
+      <c r="K17" s="5"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4"/>
-      <c r="K18" s="6"/>
+      <c r="K18" s="5"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="4"/>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="6"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="6"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="5"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="6"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="5"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="4"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="6"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="5"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="4"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="6"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="5"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="6"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="5"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="4"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="6"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="5"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="6"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="5"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5" t="s">
+      <c r="H27" t="s">
         <v>3</v>
       </c>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="6"/>
+      <c r="K27" s="5"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="7"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="9"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2188,4 +3904,1132 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6DCD075-3281-4698-9FEA-DDD7E2EDD0C9}">
+  <dimension ref="B1:M22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="4"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4"/>
+      <c r="C4" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="4"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="4"/>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="4"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="F13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="I13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="12"/>
+      <c r="K13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="39"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="39"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="4"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="39"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="4"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="39"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="39"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="4"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="39"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="39"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B18" s="4"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="39"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="39"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="4"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="15"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="15"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="4"/>
+      <c r="H21" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="6"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C4:J9"/>
+    <mergeCell ref="C13:D19"/>
+    <mergeCell ref="F13:G19"/>
+    <mergeCell ref="I13:J19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09AFEA25-EEAC-4E4B-8ACC-4F1B15B89649}">
+  <dimension ref="B1:M28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+      <c r="C3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+      <c r="C8" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="4"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="4"/>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="4"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="4"/>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="4"/>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="4"/>
+      <c r="C19" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="4"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="4"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="4"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="4"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="4"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="4"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="4"/>
+      <c r="H27" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C3:J4"/>
+    <mergeCell ref="C19:J26"/>
+    <mergeCell ref="C8:I14"/>
+    <mergeCell ref="J8:J14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD26733-85BC-4050-ABF3-378247F527A1}">
+  <dimension ref="B1:M28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+      <c r="C3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+      <c r="C8" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="4"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="4"/>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="4"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="4"/>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="4"/>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="4"/>
+      <c r="C19" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="4"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="4"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="4"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="4"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="4"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="4"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="4"/>
+      <c r="H27" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C3:J4"/>
+    <mergeCell ref="C8:I14"/>
+    <mergeCell ref="J8:J14"/>
+    <mergeCell ref="C19:J26"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14146A97-BD0A-4CDF-BF96-1D88BCB3668A}">
+  <dimension ref="B1:M28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+      <c r="C3" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+      <c r="C8" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="4"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="5"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="4"/>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="4"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="4"/>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="4"/>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="4"/>
+      <c r="C19" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="4"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="4"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="4"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="4"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="4"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="4"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="4"/>
+      <c r="H27" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C3:J4"/>
+    <mergeCell ref="C8:I14"/>
+    <mergeCell ref="J8:J14"/>
+    <mergeCell ref="C19:J26"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>